--- a/SAE_Interview_Database.xlsx
+++ b/SAE_Interview_Database.xlsx
@@ -8,19 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dhanraj Panchal\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{95400998-35A9-48AE-B708-9C76142AE1B8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B63622FE-546E-4ABC-8C6F-AF87DDAC03A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Form Responses 1" sheetId="1" r:id="rId1"/>
+    <sheet name="Candidates" sheetId="1" r:id="rId1"/>
+    <sheet name="Credentials" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8380" uniqueCount="1377">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8400" uniqueCount="1393">
   <si>
     <t>Timestamp</t>
   </si>
@@ -4151,6 +4152,54 @@
   </si>
   <si>
     <t>omkarkudalkar2016@gmail.com</t>
+  </si>
+  <si>
+    <t>Username</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>Role</t>
+  </si>
+  <si>
+    <t>Assigned Team</t>
+  </si>
+  <si>
+    <t>admin</t>
+  </si>
+  <si>
+    <t>sae_admin_2026</t>
+  </si>
+  <si>
+    <t>GC</t>
+  </si>
+  <si>
+    <t>All</t>
+  </si>
+  <si>
+    <t>miles_lead</t>
+  </si>
+  <si>
+    <t>miles123</t>
+  </si>
+  <si>
+    <t>RC</t>
+  </si>
+  <si>
+    <t>karting_lead</t>
+  </si>
+  <si>
+    <t>karting123</t>
+  </si>
+  <si>
+    <t>speedsters_lead</t>
+  </si>
+  <si>
+    <t>speedsters123</t>
+  </si>
+  <si>
+    <t>Speedsters</t>
   </si>
 </sst>
 </file>
@@ -4160,7 +4209,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="m/d/yyyy\ h:mm:ss"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -4197,6 +4246,14 @@
       <color rgb="FF0000FF"/>
       <name val="Roboto"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -4212,7 +4269,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -4415,11 +4472,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -4474,6 +4546,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -34953,4 +35028,90 @@
     <tablePart r:id="rId419"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{879C5595-5D44-404C-92D4-D17CD0F0625B}">
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="14.33203125" customWidth="1"/>
+    <col min="2" max="2" width="19.6640625" customWidth="1"/>
+    <col min="3" max="3" width="17.88671875" customWidth="1"/>
+    <col min="4" max="4" width="16.5546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4" ht="13.8" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>1377</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>1378</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>1379</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>1380</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>1381</v>
+      </c>
+      <c r="B2" t="s">
+        <v>1382</v>
+      </c>
+      <c r="C2" t="s">
+        <v>1383</v>
+      </c>
+      <c r="D2" t="s">
+        <v>1384</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>1385</v>
+      </c>
+      <c r="B3" t="s">
+        <v>1386</v>
+      </c>
+      <c r="C3" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>1388</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1389</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>1390</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1391</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1387</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1392</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/SAE_Interview_Database.xlsx
+++ b/SAE_Interview_Database.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dhanraj Panchal\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{71A03225-65A1-4FA3-A1B4-4252D05071EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FB5A17B2-0E93-4426-BA23-B83A56612DCC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{27901F35-84AC-4D18-BAE3-19840EFBC2A4}"/>
   </bookViews>
@@ -728,7 +728,7 @@
         <v>18</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>20</v>
@@ -776,7 +776,7 @@
         <v>16</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="K3" s="3" t="s">
         <v>20</v>
@@ -821,7 +821,7 @@
         <v>18</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="L4" s="3" t="s">
         <v>20</v>
@@ -860,7 +860,7 @@
         <v>17</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>20</v>
@@ -899,7 +899,7 @@
         <v>18</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="J6" s="3" t="s">
         <v>20</v>
@@ -1070,7 +1070,7 @@
         <v>17</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
       <c r="K10" s="3" t="s">
         <v>20</v>
